--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_382_R39.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_382_R39.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2752</v>
+        <v>6.0738</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6952</v>
+        <v>3.4797</v>
       </c>
       <c r="F2" t="n">
-        <v>1.58</v>
+        <v>2.5941</v>
       </c>
       <c r="G2" t="n">
-        <v>5.8935</v>
+        <v>4.5537</v>
       </c>
       <c r="H2" t="n">
-        <v>0.569</v>
+        <v>0.4666</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3246</v>
+        <v>4.0871</v>
       </c>
       <c r="J2" t="n">
-        <v>5.6958</v>
+        <v>4.2341</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0574</v>
+        <v>-0.2816</v>
       </c>
       <c r="L2" t="n">
-        <v>5.7532</v>
+        <v>4.5157</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1977</v>
+        <v>0.3196</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6263</v>
+        <v>0.7482</v>
       </c>
       <c r="O2" t="n">
         <v>-0.4286</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2275</v>
+        <v>1.8198</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.5022</v>
+        <v>-1.3648</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7297</v>
+        <v>3.1846</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4727</v>
+        <v>-0.4579</v>
       </c>
       <c r="T2" t="n">
-        <v>2.275</v>
+        <v>0.4522</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8024</v>
+        <v>-0.9101</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.3185</v>
+        <v>0.1583</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7734</v>
+        <v>0.1583</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2978</v>
+        <v>5.018</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2855</v>
+        <v>3.4381</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0123</v>
+        <v>1.58</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5537</v>
+        <v>5.8935</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4666</v>
+        <v>0.569</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0871</v>
+        <v>5.3246</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2341</v>
+        <v>5.6958</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2816</v>
+        <v>-0.0574</v>
       </c>
       <c r="L3" t="n">
-        <v>4.5157</v>
+        <v>5.7532</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3196</v>
+        <v>0.1977</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7482</v>
+        <v>0.6263</v>
       </c>
       <c r="O3" t="n">
         <v>-0.4286</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8198</v>
+        <v>0.2275</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3648</v>
+        <v>-2.5022</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1846</v>
+        <v>2.7297</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.234</v>
+        <v>0.2155</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7421</v>
+        <v>1.0178</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.4919</v>
+        <v>-0.8024</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1583</v>
+        <v>-1.3185</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1583</v>
+        <v>-0.7734</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.5451</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4965</v>
+        <v>4.7931</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4591</v>
+        <v>5.4648</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9627</v>
+        <v>-0.6718</v>
       </c>
       <c r="G4" t="n">
         <v>4.8948</v>
@@ -766,13 +766,13 @@
         <v>2.7297</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6259</v>
+        <v>-0.3293</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6943</v>
+        <v>0.3114</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9316</v>
+        <v>-0.6407</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7857</v>
+        <v>2.0602</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8269</v>
+        <v>1.1983</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9588</v>
+        <v>0.8619</v>
       </c>
       <c r="G5" t="n">
         <v>1.1742</v>
@@ -844,13 +844,13 @@
         <v>0.6824</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1565</v>
+        <v>0.431</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2932</v>
+        <v>0.6646</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1366</v>
+        <v>-0.2336</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1075</v>
+        <v>1.1326</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6884</v>
+        <v>0.4549</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4191</v>
+        <v>0.6776</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3221</v>
@@ -922,13 +922,13 @@
         <v>0.9099</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5448</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5867</v>
+        <v>0.3533</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.06710000000000001</v>
+        <v>0.1915</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6133999999999999</v>
+        <v>-0.4947</v>
       </c>
       <c r="E7" t="n">
-        <v>1.983</v>
+        <v>1.0042</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3696</v>
+        <v>-1.4989</v>
       </c>
       <c r="G7" t="n">
         <v>-1.0924</v>
@@ -1000,13 +1000,13 @@
         <v>1.8198</v>
       </c>
       <c r="S7" t="n">
-        <v>2.2245</v>
+        <v>1.1164</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6284</v>
+        <v>0.6496</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5961</v>
+        <v>0.4668</v>
       </c>
       <c r="V7" t="n">
         <v>-2.3386</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9479</v>
+        <v>-1.0574</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8789</v>
+        <v>-1.7621</v>
       </c>
       <c r="F8" t="n">
-        <v>0.931</v>
+        <v>0.7047</v>
       </c>
       <c r="G8" t="n">
         <v>0.1524</v>
@@ -1078,13 +1078,13 @@
         <v>0.2275</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1963</v>
+        <v>0.0868</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0598</v>
+        <v>0.0569</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2561</v>
+        <v>0.0299</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3867</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5344</v>
+        <v>-1.3331</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.615</v>
+        <v>-0.7803</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0806</v>
+        <v>-0.5527</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3819</v>
+        <v>-1.5665</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0561</v>
+        <v>0.018</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4381</v>
+        <v>-1.5845</v>
       </c>
       <c r="J9" t="n">
-        <v>0.495</v>
+        <v>-0.7265</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4049</v>
+        <v>0.0518</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8999</v>
+        <v>-0.7782</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.113</v>
+        <v>-0.84</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3488</v>
+        <v>-0.0338</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4618</v>
+        <v>-0.8063</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4549</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2747</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8198</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3713</v>
+        <v>0.2335</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9936</v>
+        <v>-0.0538</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6223</v>
+        <v>0.2873</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1583</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6545</v>
+        <v>-1.3742</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5584</v>
+        <v>-1.858</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9039</v>
+        <v>0.4837</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5651</v>
@@ -1234,13 +1234,13 @@
         <v>1.5923</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7733</v>
+        <v>1.0535</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0358</v>
+        <v>0.6646</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8091</v>
+        <v>0.3889</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0901</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6958</v>
+        <v>-1.4535</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0138</v>
+        <v>-1.8877</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6820000000000001</v>
+        <v>0.4342</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5665</v>
+        <v>0.3819</v>
       </c>
       <c r="H11" t="n">
-        <v>0.018</v>
+        <v>-1.0561</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5845</v>
+        <v>1.4381</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7265</v>
+        <v>0.495</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0518</v>
+        <v>-1.4049</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7782</v>
+        <v>1.8999</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.84</v>
+        <v>-0.113</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0338</v>
+        <v>0.3488</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8063</v>
+        <v>-0.4618</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.4549</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.2747</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.8198</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1293</v>
+        <v>-0.2904</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2873</v>
+        <v>-0.2662</v>
       </c>
       <c r="U11" t="n">
-        <v>0.158</v>
+        <v>-0.0241</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1583</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2485</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7246</v>
+        <v>-3.6277</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8613</v>
+        <v>-4.0229</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1366</v>
+        <v>0.3952</v>
       </c>
       <c r="G12" t="n">
         <v>-4.2443</v>
@@ -1390,13 +1390,13 @@
         <v>0.2275</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2922</v>
+        <v>0.3891</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4431</v>
+        <v>0.2815</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1509</v>
+        <v>0.1077</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.0189</v>
+        <v>9.737099999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0107</v>
+        <v>4.728999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>5.007999999999999</v>
+        <v>5.008</v>
       </c>
       <c r="G13" t="n">
         <v>8.260100000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>1.894199999999999</v>
+        <v>1.8942</v>
       </c>
       <c r="I13" t="n">
-        <v>6.366299999999998</v>
+        <v>6.3663</v>
       </c>
       <c r="J13" t="n">
         <v>10.8625</v>
@@ -1468,13 +1468,13 @@
         <v>15.9232</v>
       </c>
       <c r="S13" t="n">
-        <v>2.274700000000001</v>
+        <v>2.993</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4135</v>
+        <v>4.1319</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1389</v>
+        <v>-1.1388</v>
       </c>
       <c r="V13" t="n">
         <v>-6.0657</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8015</v>
+        <v>4.1927</v>
       </c>
       <c r="E14" t="n">
-        <v>3.113</v>
+        <v>2.2958</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6885</v>
+        <v>1.8969</v>
       </c>
       <c r="G14" t="n">
         <v>1.4645</v>
@@ -1546,13 +1546,13 @@
         <v>1.3648</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7911</v>
+        <v>1.1823</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5446</v>
+        <v>0.7275</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2464</v>
+        <v>0.4548</v>
       </c>
       <c r="V14" t="n">
         <v>1.3185</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6419</v>
+        <v>4.0247</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0609</v>
+        <v>3.7768</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.419</v>
+        <v>0.2479</v>
       </c>
       <c r="G15" t="n">
         <v>0.0815</v>
@@ -1624,13 +1624,13 @@
         <v>1.1374</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2429</v>
+        <v>0.6256</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1074</v>
+        <v>0.8233</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8645</v>
+        <v>-0.1977</v>
       </c>
       <c r="V15" t="n">
         <v>2.1802</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7219</v>
+        <v>1.8504</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1321</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8541</v>
+        <v>1.1654</v>
       </c>
       <c r="G16" t="n">
         <v>2.2</v>
@@ -1702,13 +1702,13 @@
         <v>1.5923</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6163</v>
+        <v>-0.4879</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4365</v>
+        <v>-0.6194</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1798</v>
+        <v>0.1315</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3167</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. MONEKE</t>
+          <t>T. CARTER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3611</v>
+        <v>-0.9609</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3203</v>
+        <v>-2.6714</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0408</v>
+        <v>1.7105</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.8217</v>
+        <v>0.1382</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1048</v>
+        <v>-1.7444</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.7169</v>
+        <v>1.8825</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.1554</v>
+        <v>-1.2558</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.1967</v>
+        <v>-2.2657</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0413</v>
+        <v>1.0099</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6663</v>
+        <v>1.394</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0919</v>
+        <v>0.5213</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.7582</v>
+        <v>0.8727</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6824</v>
+        <v>0.2275</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.1374</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8198</v>
+        <v>1.3648</v>
       </c>
       <c r="S18" t="n">
-        <v>0.213</v>
+        <v>-0.2364</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4073</v>
+        <v>-0.2782</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1942</v>
+        <v>0.0418</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5652</v>
+        <v>-1.0901</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5652</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. CARTER</t>
+          <t>C. MONEKE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3671</v>
+        <v>-2.185</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.2551</v>
+        <v>-1.3203</v>
       </c>
       <c r="F19" t="n">
-        <v>0.888</v>
+        <v>-0.8647</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1382</v>
+        <v>-4.8217</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7444</v>
+        <v>-2.1048</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8825</v>
+        <v>-2.7169</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2558</v>
+        <v>-2.1554</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.2657</v>
+        <v>-2.1967</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0099</v>
+        <v>0.0413</v>
       </c>
       <c r="M19" t="n">
-        <v>1.394</v>
+        <v>-2.6663</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5213</v>
+        <v>0.0919</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8727</v>
+        <v>-2.7582</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2275</v>
+        <v>0.6824</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.1374</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3648</v>
+        <v>1.8198</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6426</v>
+        <v>0.3891</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8619</v>
+        <v>0.4073</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7806999999999999</v>
+        <v>-0.0182</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0901</v>
+        <v>1.5652</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.5652</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BOLOMBOY</t>
+          <t>N. KALINIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4777</v>
+        <v>-2.6057</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3467</v>
+        <v>-1.4628</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.131</v>
+        <v>-1.1429</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5543</v>
+        <v>-3.2614</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9169</v>
+        <v>-1.1886</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6374</v>
+        <v>-2.0729</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.413</v>
+        <v>-1.2294</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4875</v>
+        <v>-0.6747</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0745</v>
+        <v>-0.5547</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1413</v>
+        <v>-2.032</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4294</v>
+        <v>-0.5138</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7119</v>
+        <v>-1.5182</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9099</v>
+        <v>1.1374</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2275</v>
+        <v>1.1374</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2131</v>
+        <v>-0.3233</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2036</v>
+        <v>-0.2333</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0095</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7734</v>
+        <v>-0.1583</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.7734</v>
+        <v>-0.1583</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. KALINIC</t>
+          <t>J. BOLOMBOY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2618</v>
+        <v>-2.9182</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1632</v>
+        <v>-2.8136</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0987</v>
+        <v>-0.1046</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.2614</v>
+        <v>-2.5543</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1886</v>
+        <v>-1.9169</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0729</v>
+        <v>-0.6374</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2294</v>
+        <v>-1.413</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6747</v>
+        <v>-1.4875</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5547</v>
+        <v>0.0745</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.032</v>
+        <v>-1.1413</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5138</v>
+        <v>-0.4294</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.5182</v>
+        <v>-0.7119</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1374</v>
+        <v>-0.9099</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1374</v>
+        <v>0.2275</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9794</v>
+        <v>-0.2275</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9337</v>
+        <v>-0.2633</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0457</v>
+        <v>0.0358</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1583</v>
+        <v>0.7734</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1583</v>
+        <v>0.7734</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. NWORA</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.827</v>
+        <v>-3.5255</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8376</v>
+        <v>-1.6551</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9894</v>
+        <v>-1.8704</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.8379</v>
+        <v>1.862</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1905</v>
+        <v>0.3638</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.0284</v>
+        <v>1.4982</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3003</v>
+        <v>4.8397</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1245</v>
+        <v>0.4276</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1758</v>
+        <v>4.4121</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5376</v>
+        <v>-2.9776</v>
       </c>
       <c r="N22" t="n">
-        <v>0.315</v>
+        <v>-0.0638</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.8526</v>
+        <v>-2.9138</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.5022</v>
+        <v>-5.2319</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4121</v>
+        <v>-6.8242</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9099</v>
+        <v>1.5923</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3328</v>
+        <v>-0.1556</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6946</v>
+        <v>0.3294</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3617</v>
+        <v>-0.485</v>
       </c>
       <c r="V22" t="n">
-        <v>2.1802</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.1802</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>J. NWORA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8281</v>
+        <v>-3.7169</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3555</v>
+        <v>-2.0711</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4725</v>
+        <v>-1.6458</v>
       </c>
       <c r="G23" t="n">
-        <v>1.862</v>
+        <v>-3.8379</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3638</v>
+        <v>0.1905</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4982</v>
+        <v>-4.0284</v>
       </c>
       <c r="J23" t="n">
-        <v>4.8397</v>
+        <v>-1.3003</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4276</v>
+        <v>-0.1245</v>
       </c>
       <c r="L23" t="n">
-        <v>4.4121</v>
+        <v>-1.1758</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.9776</v>
+        <v>-2.5376</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0638</v>
+        <v>0.315</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.9138</v>
+        <v>-2.8526</v>
       </c>
       <c r="P23" t="n">
-        <v>-5.2319</v>
+        <v>-2.5022</v>
       </c>
       <c r="Q23" t="n">
-        <v>-6.8242</v>
+        <v>-3.4121</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5923</v>
+        <v>0.9099</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4582</v>
+        <v>0.443</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.371</v>
+        <v>0.4611</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0872</v>
+        <v>-0.0181</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2.1802</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.1802</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.018899999999999</v>
+        <v>-5.905799999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.0079</v>
+        <v>-5.008000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.0109</v>
+        <v>-0.8977999999999997</v>
       </c>
       <c r="G24" t="n">
         <v>-8.260199999999998</v>
@@ -2305,7 +2305,7 @@
         <v>-3.572399999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>6.1746</v>
+        <v>6.174600000000001</v>
       </c>
       <c r="M24" t="n">
         <v>-10.8623</v>
@@ -2326,13 +2326,13 @@
         <v>11.3737</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.2747</v>
+        <v>0.8382000000000003</v>
       </c>
       <c r="T24" t="n">
         <v>1.1389</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.4135</v>
+        <v>-0.3006</v>
       </c>
       <c r="V24" t="n">
         <v>6.0657</v>
